--- a/etf_holdings/2026-09-06_errors.xlsx
+++ b/etf_holdings/2026-09-06_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:40:57</t>
+          <t>2026-09-06 21:50:14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-06 21:51:23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00400A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-09-06_errors.xlsx
+++ b/etf_holdings/2026-09-06_errors.xlsx
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:50:14</t>
+          <t>2026-09-06 22:11:14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -466,24 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-06 21:51:23</t>
+          <t>2026-09-06 22:12:54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00400A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
